--- a/obrazec.xlsx
+++ b/obrazec.xlsx
@@ -11220,39 +11220,27 @@
       <c r="DT98" s="32"/>
     </row>
     <row r="99" ht="13.5" customHeight="1" spans="2:124" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B99" s="17" t="s">
-        <v>9</v>
-      </c>
+      <c r="B99" s="17"/>
       <c r="C99" s="18"/>
       <c r="D99" s="19"/>
       <c r="E99" s="20"/>
-      <c r="F99" s="17" t="s">
-        <v>114</v>
-      </c>
+      <c r="F99" s="17"/>
       <c r="G99" s="18"/>
       <c r="H99" s="19"/>
       <c r="I99" s="20"/>
-      <c r="J99" s="17" t="s">
-        <v>30</v>
-      </c>
+      <c r="J99" s="17"/>
       <c r="K99" s="18"/>
       <c r="L99" s="19"/>
       <c r="M99" s="20"/>
-      <c r="N99" s="17" t="s">
-        <v>12</v>
-      </c>
+      <c r="N99" s="17"/>
       <c r="O99" s="18"/>
       <c r="P99" s="19"/>
       <c r="Q99" s="20"/>
-      <c r="R99" s="17" t="s">
-        <v>57</v>
-      </c>
+      <c r="R99" s="17"/>
       <c r="S99" s="18"/>
       <c r="T99" s="19"/>
       <c r="U99" s="29"/>
-      <c r="V99" s="17" t="s">
-        <v>111</v>
-      </c>
+      <c r="V99" s="17"/>
       <c r="W99" s="18"/>
       <c r="X99" s="19"/>
       <c r="Y99" s="29"/>
@@ -11483,27 +11471,39 @@
       <c r="DT100" s="32"/>
     </row>
     <row r="101" ht="13.5" customHeight="1" spans="2:124" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B101" s="17"/>
+      <c r="B101" s="17" t="s">
+        <v>9</v>
+      </c>
       <c r="C101" s="18"/>
       <c r="D101" s="19"/>
       <c r="E101" s="20"/>
-      <c r="F101" s="17"/>
+      <c r="F101" s="17" t="s">
+        <v>114</v>
+      </c>
       <c r="G101" s="18"/>
       <c r="H101" s="19"/>
       <c r="I101" s="20"/>
-      <c r="J101" s="17"/>
+      <c r="J101" s="17" t="s">
+        <v>30</v>
+      </c>
       <c r="K101" s="18"/>
       <c r="L101" s="19"/>
       <c r="M101" s="20"/>
-      <c r="N101" s="17"/>
+      <c r="N101" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="O101" s="18"/>
       <c r="P101" s="19"/>
       <c r="Q101" s="20"/>
-      <c r="R101" s="17"/>
+      <c r="R101" s="17" t="s">
+        <v>57</v>
+      </c>
       <c r="S101" s="18"/>
       <c r="T101" s="19"/>
       <c r="U101" s="29"/>
-      <c r="V101" s="17"/>
+      <c r="V101" s="17" t="s">
+        <v>111</v>
+      </c>
       <c r="W101" s="18"/>
       <c r="X101" s="19"/>
       <c r="Y101" s="29"/>
